--- a/artfynd/A 24415-2026 artfynd.xlsx
+++ b/artfynd/A 24415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416312</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>137416300</v>
       </c>
       <c r="B3" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137416309</v>
       </c>
       <c r="B4" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137416313</v>
       </c>
       <c r="B5" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137411854</v>
       </c>
       <c r="B6" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137416298</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137416299</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137416301</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137416305</v>
       </c>
       <c r="B15" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>137416308</v>
       </c>
       <c r="B16" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>137407698</v>
       </c>
       <c r="B17" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24415-2026 artfynd.xlsx
+++ b/artfynd/A 24415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416312</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>137416300</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137416309</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137416313</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137416298</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137416299</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137416301</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137416305</v>
       </c>
       <c r="B15" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>137416308</v>
       </c>
       <c r="B16" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>137407698</v>
       </c>
       <c r="B17" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24415-2026 artfynd.xlsx
+++ b/artfynd/A 24415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416312</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>137416300</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137416309</v>
       </c>
       <c r="B4" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137416313</v>
       </c>
       <c r="B5" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137416298</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137416299</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137416301</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137416305</v>
       </c>
       <c r="B15" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>137416308</v>
       </c>
       <c r="B16" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>137407698</v>
       </c>
       <c r="B17" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 24415-2026 artfynd.xlsx
+++ b/artfynd/A 24415-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137416312</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>137416300</v>
       </c>
       <c r="B3" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137416309</v>
       </c>
       <c r="B4" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137416313</v>
       </c>
       <c r="B5" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137411854</v>
       </c>
       <c r="B6" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>137416298</v>
       </c>
       <c r="B7" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137416299</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137416301</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>137416303</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>137416310</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137416314</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>137416295</v>
       </c>
       <c r="B13" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>137416311</v>
       </c>
       <c r="B14" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>137416305</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>137416308</v>
       </c>
       <c r="B16" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>137407698</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
